--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260918.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260918.xlsx
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>1,371,000</t>
+          <t>99,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>99,000</t>
+          <t>1,371,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>571,000</t>
+          <t>435,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>435,000</t>
+          <t>571,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>202610WVHFV6F</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>2,166,107</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>202610WVHFV6F</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>2,166,107</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>328,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>169,000</t>
+          <t>328,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>63,538</t>
+          <t>169,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>63,538</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>672,000</t>
+          <t>155,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>155,000</t>
+          <t>672,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
